--- a/Produce/xls/MonsterConfig.xlsx
+++ b/Produce/xls/MonsterConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12465"/>
+    <workbookView windowWidth="28125" windowHeight="12690"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterBaseConfig" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -31,6 +31,15 @@
     <t>#AttrDic</t>
   </si>
   <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>Atk</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -40,6 +49,12 @@
     <t>Dictionary&lt;int,float&gt;</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -52,7 +67,16 @@
     <t>初始属性字典</t>
   </si>
   <si>
-    <t>蓄力一击</t>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>初始技能数组</t>
+  </si>
+  <si>
+    <t>骑士</t>
   </si>
   <si>
     <t>双倍伤害</t>
@@ -61,7 +85,10 @@
     <t>{1,20:2,10}</t>
   </si>
   <si>
-    <t>强力护盾</t>
+    <t>[1001,1002]</t>
+  </si>
+  <si>
+    <t>大法师</t>
   </si>
   <si>
     <t>抵挡伤害</t>
@@ -94,6 +121,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -101,69 +136,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -194,14 +213,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -209,30 +220,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,181 +292,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,16 +481,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -483,28 +519,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,26 +561,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -558,145 +585,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1061,15 +1088,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="31.5" customWidth="1"/>
     <col min="3" max="3" width="38.125" customWidth="1"/>
     <col min="4" max="5" width="22.875" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,71 +1115,116 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:8">
       <c r="A4" s="3">
         <v>1001</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F4" s="3">
+        <v>20</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:8">
       <c r="A5" s="3">
         <v>1002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F5" s="3">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3">
+        <v>8</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
